--- a/planilla/La-ONCE-planilla.xlsx
+++ b/planilla/La-ONCE-planilla.xlsx
@@ -203,7 +203,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="111">
   <si>
-    <t xml:space="preserve">Planilla de La ONCE Kits</t>
+    <t xml:space="preserve">Planilla de La ONCE Avellaneda</t>
   </si>
   <si>
     <t xml:space="preserve">Qué hay en cada pestaña</t>
